--- a/Excel/JiaYuanConfig.xlsx
+++ b/Excel/JiaYuanConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93358829-D43E-49DE-8F52-48E9557E784F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE57DA6-0F92-4117-9549-EA3553C20222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JiaYuanProto" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="189">
   <si>
     <t>Id</t>
   </si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>FarmNumMax</t>
-  </si>
-  <si>
-    <t>JiaYuanDes</t>
   </si>
   <si>
     <t>ExchangeExpCostZiJin</t>
@@ -443,6 +440,177 @@
   </si>
   <si>
     <t>100403,1550;100603,465;100803,465;100203,15500;119303,775;119403,775;119103,775;119203,775;105103,155;105303,155;105203,155;105403,155;105503,155;119503,775;110203,465;110103,775;120603,465;120703,465</t>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Home Level: 1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Home Level: 2</t>
+  </si>
+  <si>
+    <t>Home Level: 3</t>
+  </si>
+  <si>
+    <t>Home Level: 4</t>
+  </si>
+  <si>
+    <t>Home Level: 5</t>
+  </si>
+  <si>
+    <t>Home Level: 6</t>
+  </si>
+  <si>
+    <t>Home Level: 7</t>
+  </si>
+  <si>
+    <t>Home Level: 8</t>
+  </si>
+  <si>
+    <t>Home Level: 9</t>
+  </si>
+  <si>
+    <t>Home Level: 10</t>
+  </si>
+  <si>
+    <t>Home Level: 11</t>
+  </si>
+  <si>
+    <t>Home Level: 12</t>
+  </si>
+  <si>
+    <t>Home Level: 13</t>
+  </si>
+  <si>
+    <t>Home Level: 14</t>
+  </si>
+  <si>
+    <t>Home Level: 15</t>
+  </si>
+  <si>
+    <t>Home Level: 16</t>
+  </si>
+  <si>
+    <t>Home Level: 17</t>
+  </si>
+  <si>
+    <t>Home Level: 18</t>
+  </si>
+  <si>
+    <t>Home Level: 19</t>
+  </si>
+  <si>
+    <t>Home Level: 20</t>
+  </si>
+  <si>
+    <t>Home Level: 21</t>
+  </si>
+  <si>
+    <t>Home Level: 22</t>
+  </si>
+  <si>
+    <t>Home Level: 23</t>
+  </si>
+  <si>
+    <t>Home Level: 24</t>
+  </si>
+  <si>
+    <t>Home Level: 25</t>
+  </si>
+  <si>
+    <t>Home Level: 26</t>
+  </si>
+  <si>
+    <t>Home Level: 27</t>
+  </si>
+  <si>
+    <t>Home Level: 28</t>
+  </si>
+  <si>
+    <t>Home Level: 29</t>
+  </si>
+  <si>
+    <t>Home Level: 30</t>
+  </si>
+  <si>
+    <t>JiaYuanDes</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>JiaYuanDes_EN</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 5; Cultivation limit increased to 5; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 6; Cultivation limit increased to 6; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 7; Cultivation limit increased to 7; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 8; Cultivation limit increased to 8; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 9; Cultivation limit increased to 9; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 10; Cultivation limit increased to 10; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 11; Cultivation limit increased to 11; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 12; Cultivation limit increased to 12; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 13; Cultivation limit increased to 13; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 14; Cultivation limit increased to 14; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 15; Cultivation limit increased to 15; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 16; Cultivation limit increased to 16; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 17; Cultivation limit increased to 17; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 18; Cultivation limit increased to 18; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 19; Cultivation limit increased to 19; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Population limit increased to 20; Cultivation limit increased to 20; Unlock higher-level cooking</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -637,7 +805,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -727,6 +895,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </left>
+      <right style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1660,7 +1841,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1711,6 +1892,10 @@
     <xf numFmtId="0" fontId="5" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="314">
     <cellStyle name="20% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -2354,38 +2539,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:U50"/>
+  <dimension ref="C1:W50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="17.875" customWidth="1"/>
-    <col min="5" max="5" width="17.25" customWidth="1"/>
-    <col min="6" max="7" width="17.875" customWidth="1"/>
-    <col min="8" max="8" width="17.25" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="17.25" customWidth="1"/>
-    <col min="11" max="11" width="48.5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.875" customWidth="1"/>
-    <col min="13" max="17" width="17.25" customWidth="1"/>
-    <col min="18" max="18" width="28.375" customWidth="1"/>
-    <col min="19" max="23" width="10.875" customWidth="1"/>
+    <col min="4" max="5" width="17.875" customWidth="1"/>
+    <col min="6" max="6" width="17.25" customWidth="1"/>
+    <col min="7" max="8" width="17.875" customWidth="1"/>
+    <col min="9" max="9" width="17.25" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="17.25" customWidth="1"/>
+    <col min="12" max="12" width="48.5" style="2" customWidth="1"/>
+    <col min="13" max="13" width="91.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.875" customWidth="1"/>
+    <col min="15" max="19" width="17.25" customWidth="1"/>
+    <col min="20" max="20" width="28.375" customWidth="1"/>
+    <col min="21" max="25" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:21" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E1"/>
-      <c r="H1"/>
-      <c r="J1"/>
-      <c r="K1" s="10"/>
-      <c r="L1"/>
-      <c r="M1"/>
+    <row r="1" spans="3:23" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F1"/>
+      <c r="I1"/>
+      <c r="K1"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
       <c r="N1"/>
       <c r="O1"/>
       <c r="P1"/>
       <c r="Q1"/>
       <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
     </row>
-    <row r="2" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E2" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2393,49 +2584,55 @@
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="R3" s="4" t="s">
+      <c r="S3" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="T3" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -2443,75 +2640,81 @@
         <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="R4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="S4" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="T4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="R4" s="4" t="s">
+    </row>
+    <row r="5" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>29</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>29</v>
@@ -2520,1573 +2723,1759 @@
         <v>29</v>
       </c>
       <c r="N5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="T5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="6" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="6">
         <v>10001</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="6">
+        <v>10002</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="6">
-        <v>10002</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="H6" s="8">
+        <v>5000</v>
+      </c>
+      <c r="I6" s="6">
+        <v>5</v>
+      </c>
+      <c r="J6" s="8">
+        <v>5</v>
+      </c>
+      <c r="K6" s="6">
+        <v>5</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="8">
-        <v>5000</v>
-      </c>
-      <c r="H6" s="6">
-        <v>5</v>
-      </c>
-      <c r="I6" s="8">
-        <v>5</v>
-      </c>
-      <c r="J6" s="6">
-        <v>5</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6" s="6">
+      <c r="M6" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="N6" s="6">
         <v>9000</v>
       </c>
-      <c r="M6" s="6">
+      <c r="O6" s="6">
         <v>1000</v>
       </c>
-      <c r="N6" s="6">
+      <c r="P6" s="6">
         <v>150000</v>
       </c>
-      <c r="O6" s="6">
+      <c r="Q6" s="6">
         <v>8000</v>
       </c>
-      <c r="P6" s="6">
+      <c r="R6" s="6">
         <v>420</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="S6" s="6">
         <v>1</v>
       </c>
-      <c r="R6" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="U6" s="11"/>
+      <c r="T6" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="W6" s="11"/>
     </row>
-    <row r="7" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="6">
         <v>10002</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F7" s="6">
+        <v>10003</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="6">
-        <v>10003</v>
-      </c>
-      <c r="F7" s="7" t="s">
+      <c r="H7" s="8">
+        <v>6600</v>
+      </c>
+      <c r="I7" s="6">
+        <v>6</v>
+      </c>
+      <c r="J7" s="8">
+        <v>10</v>
+      </c>
+      <c r="K7" s="6">
+        <v>6</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="8">
-        <v>6600</v>
-      </c>
-      <c r="H7" s="6">
-        <v>6</v>
-      </c>
-      <c r="I7" s="8">
-        <v>10</v>
-      </c>
-      <c r="J7" s="6">
-        <v>6</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="6">
+      <c r="M7" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="N7" s="6">
         <v>11250</v>
       </c>
-      <c r="M7" s="6">
+      <c r="O7" s="6">
         <v>1100</v>
       </c>
-      <c r="N7" s="6">
+      <c r="P7" s="6">
         <v>160000</v>
       </c>
-      <c r="O7" s="6">
+      <c r="Q7" s="6">
         <v>9000</v>
       </c>
-      <c r="P7" s="6">
+      <c r="R7" s="6">
         <v>460</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="S7" s="6">
         <v>1</v>
       </c>
-      <c r="R7" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="U7" s="11"/>
+      <c r="T7" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="W7" s="11"/>
     </row>
-    <row r="8" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="6">
         <v>10003</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F8" s="6">
+        <v>10004</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="6">
-        <v>10004</v>
-      </c>
-      <c r="F8" s="7" t="s">
+      <c r="H8" s="8">
+        <v>8400</v>
+      </c>
+      <c r="I8" s="6">
+        <v>7</v>
+      </c>
+      <c r="J8" s="8">
+        <v>15</v>
+      </c>
+      <c r="K8" s="6">
+        <v>7</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="8">
-        <v>8400</v>
-      </c>
-      <c r="H8" s="6">
-        <v>7</v>
-      </c>
-      <c r="I8" s="8">
-        <v>15</v>
-      </c>
-      <c r="J8" s="6">
-        <v>7</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="6">
+      <c r="M8" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="N8" s="6">
         <v>13500</v>
       </c>
-      <c r="M8" s="6">
+      <c r="O8" s="6">
         <v>1200</v>
       </c>
-      <c r="N8" s="6">
+      <c r="P8" s="6">
         <v>170000</v>
       </c>
-      <c r="O8" s="6">
+      <c r="Q8" s="6">
         <v>10000</v>
       </c>
-      <c r="P8" s="6">
+      <c r="R8" s="6">
         <v>500</v>
       </c>
-      <c r="Q8" s="6">
+      <c r="S8" s="6">
         <v>1</v>
       </c>
-      <c r="R8" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="U8" s="11"/>
+      <c r="T8" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="W8" s="11"/>
     </row>
-    <row r="9" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="6">
         <v>10004</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F9" s="6">
+        <v>10005</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="6">
-        <v>10005</v>
-      </c>
-      <c r="F9" s="7" t="s">
+      <c r="H9" s="8">
+        <v>11700</v>
+      </c>
+      <c r="I9" s="6">
+        <v>8</v>
+      </c>
+      <c r="J9" s="8">
+        <v>20</v>
+      </c>
+      <c r="K9" s="6">
+        <v>8</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="8">
-        <v>11700</v>
-      </c>
-      <c r="H9" s="6">
-        <v>8</v>
-      </c>
-      <c r="I9" s="8">
-        <v>20</v>
-      </c>
-      <c r="J9" s="6">
-        <v>8</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9" s="6">
+      <c r="M9" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="N9" s="6">
         <v>15750</v>
       </c>
-      <c r="M9" s="6">
+      <c r="O9" s="6">
         <v>1300</v>
       </c>
-      <c r="N9" s="6">
+      <c r="P9" s="6">
         <v>180000</v>
       </c>
-      <c r="O9" s="6">
+      <c r="Q9" s="6">
         <v>11000</v>
       </c>
-      <c r="P9" s="6">
+      <c r="R9" s="6">
         <v>540</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="S9" s="6">
         <v>1</v>
       </c>
-      <c r="R9" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="U9" s="11"/>
+      <c r="T9" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="W9" s="11"/>
     </row>
-    <row r="10" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="6">
         <v>10005</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="F10" s="6">
+        <v>10006</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="6">
-        <v>10006</v>
-      </c>
-      <c r="F10" s="7" t="s">
+      <c r="H10" s="8">
+        <v>15400</v>
+      </c>
+      <c r="I10" s="6">
+        <v>9</v>
+      </c>
+      <c r="J10" s="8">
+        <v>25</v>
+      </c>
+      <c r="K10" s="6">
+        <v>9</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="8">
-        <v>15400</v>
-      </c>
-      <c r="H10" s="6">
-        <v>9</v>
-      </c>
-      <c r="I10" s="8">
-        <v>25</v>
-      </c>
-      <c r="J10" s="6">
-        <v>9</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10" s="6">
+      <c r="M10" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="N10" s="6">
         <v>18000</v>
       </c>
-      <c r="M10" s="6">
+      <c r="O10" s="6">
         <v>1400</v>
       </c>
-      <c r="N10" s="6">
+      <c r="P10" s="6">
         <v>190000</v>
       </c>
-      <c r="O10" s="6">
+      <c r="Q10" s="6">
         <v>12000</v>
       </c>
-      <c r="P10" s="6">
+      <c r="R10" s="6">
         <v>580</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="S10" s="6">
         <v>1</v>
       </c>
-      <c r="R10" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="U10" s="11"/>
+      <c r="T10" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="W10" s="11"/>
     </row>
-    <row r="11" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="6">
         <v>10006</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="F11" s="6">
+        <v>10007</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="6">
-        <v>10007</v>
-      </c>
-      <c r="F11" s="7" t="s">
+      <c r="H11" s="8">
+        <v>21000</v>
+      </c>
+      <c r="I11" s="6">
+        <v>10</v>
+      </c>
+      <c r="J11" s="8">
+        <v>30</v>
+      </c>
+      <c r="K11" s="6">
+        <v>10</v>
+      </c>
+      <c r="L11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="8">
-        <v>21000</v>
-      </c>
-      <c r="H11" s="6">
-        <v>10</v>
-      </c>
-      <c r="I11" s="8">
-        <v>30</v>
-      </c>
-      <c r="J11" s="6">
-        <v>10</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="M11" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="N11" s="6">
         <v>20250</v>
       </c>
-      <c r="M11" s="6">
+      <c r="O11" s="6">
         <v>1500</v>
       </c>
-      <c r="N11" s="6">
+      <c r="P11" s="6">
         <v>200000</v>
       </c>
-      <c r="O11" s="6">
+      <c r="Q11" s="6">
         <v>13500</v>
       </c>
-      <c r="P11" s="6">
+      <c r="R11" s="6">
         <v>630</v>
       </c>
-      <c r="Q11" s="6">
+      <c r="S11" s="6">
         <v>2</v>
       </c>
-      <c r="R11" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="U11" s="11"/>
+      <c r="T11" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="W11" s="11"/>
     </row>
-    <row r="12" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="6">
         <v>10007</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" s="6">
+        <v>10008</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="6">
-        <v>10008</v>
-      </c>
-      <c r="F12" s="7" t="s">
+      <c r="H12" s="8">
+        <v>27200</v>
+      </c>
+      <c r="I12" s="6">
+        <v>11</v>
+      </c>
+      <c r="J12" s="8">
+        <v>35</v>
+      </c>
+      <c r="K12" s="6">
+        <v>11</v>
+      </c>
+      <c r="L12" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="8">
-        <v>27200</v>
-      </c>
-      <c r="H12" s="6">
-        <v>11</v>
-      </c>
-      <c r="I12" s="8">
-        <v>35</v>
-      </c>
-      <c r="J12" s="6">
-        <v>11</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="L12" s="6">
+      <c r="M12" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="N12" s="6">
         <v>22500</v>
       </c>
-      <c r="M12" s="6">
+      <c r="O12" s="6">
         <v>1600</v>
       </c>
-      <c r="N12" s="6">
+      <c r="P12" s="6">
         <v>200000</v>
       </c>
-      <c r="O12" s="6">
+      <c r="Q12" s="6">
         <v>15000</v>
       </c>
-      <c r="P12" s="6">
+      <c r="R12" s="6">
         <v>670</v>
       </c>
-      <c r="Q12" s="6">
+      <c r="S12" s="6">
         <v>2</v>
       </c>
-      <c r="R12" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="U12" s="11"/>
+      <c r="T12" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="W12" s="11"/>
     </row>
-    <row r="13" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="6">
         <v>10008</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="6">
+        <v>10009</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="6">
-        <v>10009</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="H13" s="8">
+        <v>35700</v>
+      </c>
+      <c r="I13" s="6">
+        <v>12</v>
+      </c>
+      <c r="J13" s="8">
+        <v>40</v>
+      </c>
+      <c r="K13" s="6">
+        <v>12</v>
+      </c>
+      <c r="L13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="8">
-        <v>35700</v>
-      </c>
-      <c r="H13" s="6">
-        <v>12</v>
-      </c>
-      <c r="I13" s="8">
-        <v>40</v>
-      </c>
-      <c r="J13" s="6">
-        <v>12</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="L13" s="6">
+      <c r="M13" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="N13" s="6">
         <v>24750</v>
       </c>
-      <c r="M13" s="6">
+      <c r="O13" s="6">
         <v>1700</v>
       </c>
-      <c r="N13" s="6">
+      <c r="P13" s="6">
         <v>200000</v>
       </c>
-      <c r="O13" s="6">
+      <c r="Q13" s="6">
         <v>16500</v>
       </c>
-      <c r="P13" s="6">
+      <c r="R13" s="6">
         <v>710</v>
       </c>
-      <c r="Q13" s="6">
+      <c r="S13" s="6">
         <v>2</v>
       </c>
-      <c r="R13" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="U13" s="11"/>
+      <c r="T13" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="W13" s="11"/>
     </row>
-    <row r="14" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="6">
         <v>10009</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F14" s="6">
+        <v>10010</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="6">
-        <v>10010</v>
-      </c>
-      <c r="F14" s="7" t="s">
+      <c r="H14" s="8">
+        <v>45000</v>
+      </c>
+      <c r="I14" s="6">
+        <v>13</v>
+      </c>
+      <c r="J14" s="8">
+        <v>45</v>
+      </c>
+      <c r="K14" s="6">
+        <v>13</v>
+      </c>
+      <c r="L14" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="8">
-        <v>45000</v>
-      </c>
-      <c r="H14" s="6">
-        <v>13</v>
-      </c>
-      <c r="I14" s="8">
-        <v>45</v>
-      </c>
-      <c r="J14" s="6">
-        <v>13</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="L14" s="6">
+      <c r="M14" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="N14" s="6">
         <v>27000</v>
       </c>
-      <c r="M14" s="6">
+      <c r="O14" s="6">
         <v>1800</v>
       </c>
-      <c r="N14" s="6">
+      <c r="P14" s="6">
         <v>200000</v>
       </c>
-      <c r="O14" s="6">
+      <c r="Q14" s="6">
         <v>18000</v>
       </c>
-      <c r="P14" s="6">
+      <c r="R14" s="6">
         <v>750</v>
       </c>
-      <c r="Q14" s="6">
+      <c r="S14" s="6">
         <v>2</v>
       </c>
-      <c r="R14" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="U14" s="11"/>
+      <c r="T14" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="W14" s="11"/>
     </row>
-    <row r="15" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="6">
         <v>10010</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F15" s="6">
+        <v>10011</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="6">
-        <v>10011</v>
-      </c>
-      <c r="F15" s="7" t="s">
+      <c r="H15" s="8">
+        <v>57000</v>
+      </c>
+      <c r="I15" s="6">
+        <v>14</v>
+      </c>
+      <c r="J15" s="8">
+        <v>50</v>
+      </c>
+      <c r="K15" s="6">
+        <v>14</v>
+      </c>
+      <c r="L15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="8">
-        <v>57000</v>
-      </c>
-      <c r="H15" s="6">
-        <v>14</v>
-      </c>
-      <c r="I15" s="8">
-        <v>50</v>
-      </c>
-      <c r="J15" s="6">
-        <v>14</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15" s="6">
+      <c r="M15" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="N15" s="6">
         <v>29250</v>
       </c>
-      <c r="M15" s="6">
+      <c r="O15" s="6">
         <v>1900</v>
       </c>
-      <c r="N15" s="6">
+      <c r="P15" s="6">
         <v>200000</v>
       </c>
-      <c r="O15" s="6">
+      <c r="Q15" s="6">
         <v>19500</v>
       </c>
-      <c r="P15" s="6">
+      <c r="R15" s="6">
         <v>790</v>
       </c>
-      <c r="Q15" s="6">
+      <c r="S15" s="6">
         <v>2</v>
       </c>
-      <c r="R15" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="U15" s="11"/>
+      <c r="T15" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="W15" s="11"/>
     </row>
-    <row r="16" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="6">
         <v>10011</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="F16" s="6">
+        <v>10012</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="6">
-        <v>10012</v>
-      </c>
-      <c r="F16" s="7" t="s">
+      <c r="H16" s="8">
+        <v>70000</v>
+      </c>
+      <c r="I16" s="6">
+        <v>15</v>
+      </c>
+      <c r="J16" s="8">
+        <v>50</v>
+      </c>
+      <c r="K16" s="6">
+        <v>15</v>
+      </c>
+      <c r="L16" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="8">
-        <v>70000</v>
-      </c>
-      <c r="H16" s="6">
-        <v>15</v>
-      </c>
-      <c r="I16" s="8">
-        <v>50</v>
-      </c>
-      <c r="J16" s="6">
-        <v>15</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="L16" s="6">
+      <c r="M16" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="N16" s="6">
         <v>31500</v>
       </c>
-      <c r="M16" s="6">
+      <c r="O16" s="6">
         <v>2000</v>
       </c>
-      <c r="N16" s="6">
+      <c r="P16" s="6">
         <v>200000</v>
       </c>
-      <c r="O16" s="6">
+      <c r="Q16" s="6">
         <v>21000</v>
       </c>
-      <c r="P16" s="6">
+      <c r="R16" s="6">
         <v>830</v>
       </c>
-      <c r="Q16" s="6">
+      <c r="S16" s="6">
         <v>2</v>
       </c>
-      <c r="R16" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="U16" s="11"/>
+      <c r="T16" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="W16" s="11"/>
     </row>
-    <row r="17" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="6">
         <v>10012</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="F17" s="6">
+        <v>10013</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="6">
-        <v>10013</v>
-      </c>
-      <c r="F17" s="7" t="s">
+      <c r="H17" s="8">
+        <v>86100</v>
+      </c>
+      <c r="I17" s="6">
+        <v>16</v>
+      </c>
+      <c r="J17" s="8">
+        <v>50</v>
+      </c>
+      <c r="K17" s="6">
+        <v>16</v>
+      </c>
+      <c r="L17" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="8">
-        <v>86100</v>
-      </c>
-      <c r="H17" s="6">
-        <v>16</v>
-      </c>
-      <c r="I17" s="8">
-        <v>50</v>
-      </c>
-      <c r="J17" s="6">
-        <v>16</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L17" s="6">
+      <c r="M17" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="N17" s="6">
         <v>33750</v>
       </c>
-      <c r="M17" s="6">
+      <c r="O17" s="6">
         <v>2100</v>
       </c>
-      <c r="N17" s="6">
+      <c r="P17" s="6">
         <v>200000</v>
       </c>
-      <c r="O17" s="6">
+      <c r="Q17" s="6">
         <v>22500</v>
       </c>
-      <c r="P17" s="6">
+      <c r="R17" s="6">
         <v>880</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="S17" s="6">
         <v>3</v>
       </c>
-      <c r="R17" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="U17" s="11"/>
+      <c r="T17" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="W17" s="11"/>
     </row>
-    <row r="18" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="6">
         <v>10013</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F18" s="6">
+        <v>10014</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="6">
-        <v>10014</v>
-      </c>
-      <c r="F18" s="7" t="s">
+      <c r="H18" s="8">
+        <v>103400</v>
+      </c>
+      <c r="I18" s="6">
+        <v>17</v>
+      </c>
+      <c r="J18" s="8">
+        <v>50</v>
+      </c>
+      <c r="K18" s="6">
+        <v>17</v>
+      </c>
+      <c r="L18" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G18" s="8">
-        <v>103400</v>
-      </c>
-      <c r="H18" s="6">
-        <v>17</v>
-      </c>
-      <c r="I18" s="8">
-        <v>50</v>
-      </c>
-      <c r="J18" s="6">
-        <v>17</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="L18" s="6">
+      <c r="M18" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="N18" s="6">
         <v>36000</v>
       </c>
-      <c r="M18" s="6">
+      <c r="O18" s="6">
         <v>2200</v>
       </c>
-      <c r="N18" s="6">
+      <c r="P18" s="6">
         <v>200000</v>
       </c>
-      <c r="O18" s="6">
+      <c r="Q18" s="6">
         <v>24000</v>
       </c>
-      <c r="P18" s="6">
+      <c r="R18" s="6">
         <v>920</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="S18" s="6">
         <v>3</v>
       </c>
-      <c r="R18" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="U18" s="11"/>
+      <c r="T18" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="W18" s="11"/>
     </row>
-    <row r="19" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="6">
         <v>10014</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" s="6">
+        <v>10015</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="6">
-        <v>10015</v>
-      </c>
-      <c r="F19" s="7" t="s">
+      <c r="H19" s="8">
+        <v>124200</v>
+      </c>
+      <c r="I19" s="6">
+        <v>18</v>
+      </c>
+      <c r="J19" s="8">
+        <v>50</v>
+      </c>
+      <c r="K19" s="6">
+        <v>18</v>
+      </c>
+      <c r="L19" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="8">
-        <v>124200</v>
-      </c>
-      <c r="H19" s="6">
-        <v>18</v>
-      </c>
-      <c r="I19" s="8">
-        <v>50</v>
-      </c>
-      <c r="J19" s="6">
-        <v>18</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="L19" s="6">
+      <c r="M19" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="N19" s="6">
         <v>39000</v>
       </c>
-      <c r="M19" s="6">
+      <c r="O19" s="6">
         <v>2300</v>
       </c>
-      <c r="N19" s="6">
+      <c r="P19" s="6">
         <v>200000</v>
       </c>
-      <c r="O19" s="6">
+      <c r="Q19" s="6">
         <v>26000</v>
       </c>
-      <c r="P19" s="6">
+      <c r="R19" s="6">
         <v>960</v>
       </c>
-      <c r="Q19" s="6">
+      <c r="S19" s="6">
         <v>3</v>
       </c>
-      <c r="R19" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="U19" s="11"/>
+      <c r="T19" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="W19" s="11"/>
     </row>
-    <row r="20" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="6">
         <v>10015</v>
       </c>
       <c r="D20" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="F20" s="6">
+        <v>10016</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="6">
-        <v>10016</v>
-      </c>
-      <c r="F20" s="7" t="s">
+      <c r="H20" s="8">
+        <v>146400</v>
+      </c>
+      <c r="I20" s="6">
+        <v>19</v>
+      </c>
+      <c r="J20" s="8">
+        <v>50</v>
+      </c>
+      <c r="K20" s="6">
+        <v>19</v>
+      </c>
+      <c r="L20" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G20" s="8">
-        <v>146400</v>
-      </c>
-      <c r="H20" s="6">
-        <v>19</v>
-      </c>
-      <c r="I20" s="8">
-        <v>50</v>
-      </c>
-      <c r="J20" s="6">
-        <v>19</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="L20" s="6">
+      <c r="M20" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="N20" s="6">
         <v>42000</v>
       </c>
-      <c r="M20" s="6">
+      <c r="O20" s="6">
         <v>2400</v>
       </c>
-      <c r="N20" s="6">
+      <c r="P20" s="6">
         <v>200000</v>
       </c>
-      <c r="O20" s="6">
+      <c r="Q20" s="6">
         <v>28000</v>
       </c>
-      <c r="P20" s="6">
+      <c r="R20" s="6">
         <v>1000</v>
       </c>
-      <c r="Q20" s="6">
+      <c r="S20" s="6">
         <v>4</v>
       </c>
-      <c r="R20" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="U20" s="11"/>
+      <c r="T20" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="W20" s="11"/>
     </row>
-    <row r="21" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="6">
         <v>10016</v>
       </c>
       <c r="D21" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F21" s="6">
+        <v>10017</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="6">
-        <v>10017</v>
-      </c>
-      <c r="F21" s="7" t="s">
+      <c r="H21" s="8">
+        <v>172500</v>
+      </c>
+      <c r="I21" s="6">
+        <v>20</v>
+      </c>
+      <c r="J21" s="8">
+        <v>50</v>
+      </c>
+      <c r="K21" s="6">
+        <v>20</v>
+      </c>
+      <c r="L21" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="8">
-        <v>172500</v>
-      </c>
-      <c r="H21" s="6">
-        <v>20</v>
-      </c>
-      <c r="I21" s="8">
-        <v>50</v>
-      </c>
-      <c r="J21" s="6">
-        <v>20</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L21" s="6">
+      <c r="M21" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N21" s="6">
         <v>45000</v>
       </c>
-      <c r="M21" s="6">
+      <c r="O21" s="6">
         <v>2500</v>
       </c>
-      <c r="N21" s="6">
+      <c r="P21" s="6">
         <v>200000</v>
       </c>
-      <c r="O21" s="6">
+      <c r="Q21" s="6">
         <v>30000</v>
       </c>
-      <c r="P21" s="6">
+      <c r="R21" s="6">
         <v>1040</v>
       </c>
-      <c r="Q21" s="6">
+      <c r="S21" s="6">
         <v>4</v>
       </c>
-      <c r="R21" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="U21" s="11"/>
+      <c r="T21" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="W21" s="11"/>
     </row>
-    <row r="22" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C22" s="6">
         <v>10017</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="F22" s="6">
+        <v>10018</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="6">
-        <v>10018</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G22" s="8">
+      <c r="H22" s="8">
         <v>200200</v>
       </c>
-      <c r="H22" s="6">
+      <c r="I22" s="6">
         <v>20</v>
       </c>
-      <c r="I22" s="8">
+      <c r="J22" s="8">
         <v>50</v>
       </c>
-      <c r="J22" s="6">
+      <c r="K22" s="6">
         <v>20</v>
       </c>
-      <c r="K22" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L22" s="6">
+      <c r="L22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N22" s="6">
         <v>48000</v>
       </c>
-      <c r="M22" s="6">
+      <c r="O22" s="6">
         <v>2600</v>
       </c>
-      <c r="N22" s="6">
+      <c r="P22" s="6">
         <v>200000</v>
       </c>
-      <c r="O22" s="6">
+      <c r="Q22" s="6">
         <v>32000</v>
       </c>
-      <c r="P22" s="6">
+      <c r="R22" s="6">
         <v>1080</v>
       </c>
-      <c r="Q22" s="6">
+      <c r="S22" s="6">
         <v>4</v>
       </c>
-      <c r="R22" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="U22" s="11"/>
+      <c r="T22" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="W22" s="11"/>
     </row>
-    <row r="23" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="6">
         <v>10018</v>
       </c>
       <c r="D23" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="F23" s="6">
+        <v>10019</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="6">
-        <v>10019</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="8">
+      <c r="H23" s="8">
         <v>232200</v>
       </c>
-      <c r="H23" s="6">
+      <c r="I23" s="6">
         <v>20</v>
       </c>
-      <c r="I23" s="8">
+      <c r="J23" s="8">
         <v>50</v>
       </c>
-      <c r="J23" s="6">
+      <c r="K23" s="6">
         <v>20</v>
       </c>
-      <c r="K23" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L23" s="6">
+      <c r="L23" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N23" s="6">
         <v>52500</v>
       </c>
-      <c r="M23" s="6">
+      <c r="O23" s="6">
         <v>2700</v>
       </c>
-      <c r="N23" s="6">
+      <c r="P23" s="6">
         <v>200000</v>
       </c>
-      <c r="O23" s="6">
+      <c r="Q23" s="6">
         <v>34000</v>
       </c>
-      <c r="P23" s="6">
+      <c r="R23" s="6">
         <v>1130</v>
       </c>
-      <c r="Q23" s="6">
+      <c r="S23" s="6">
         <v>5</v>
       </c>
-      <c r="R23" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="U23" s="11"/>
+      <c r="T23" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="W23" s="11"/>
     </row>
-    <row r="24" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="6">
         <v>10019</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="6">
+        <v>10020</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="6">
-        <v>10020</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" s="8">
+      <c r="H24" s="8">
         <v>266000</v>
       </c>
-      <c r="H24" s="6">
+      <c r="I24" s="6">
         <v>20</v>
       </c>
-      <c r="I24" s="8">
+      <c r="J24" s="8">
         <v>50</v>
       </c>
-      <c r="J24" s="6">
+      <c r="K24" s="6">
         <v>20</v>
       </c>
-      <c r="K24" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L24" s="6">
+      <c r="L24" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N24" s="6">
         <v>58500</v>
       </c>
-      <c r="M24" s="6">
+      <c r="O24" s="6">
         <v>2800</v>
       </c>
-      <c r="N24" s="6">
+      <c r="P24" s="6">
         <v>200000</v>
       </c>
-      <c r="O24" s="6">
+      <c r="Q24" s="6">
         <v>36000</v>
       </c>
-      <c r="P24" s="6">
+      <c r="R24" s="6">
         <v>1170</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="S24" s="6">
         <v>5</v>
       </c>
-      <c r="R24" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="U24" s="11"/>
+      <c r="T24" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="W24" s="11"/>
     </row>
-    <row r="25" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="6">
         <v>10020</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="F25" s="6">
+        <v>10021</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="6">
-        <v>10021</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" s="8">
+      <c r="H25" s="8">
         <v>304500</v>
       </c>
-      <c r="H25" s="6">
+      <c r="I25" s="6">
         <v>20</v>
       </c>
-      <c r="I25" s="8">
+      <c r="J25" s="8">
         <v>50</v>
       </c>
-      <c r="J25" s="6">
+      <c r="K25" s="6">
         <v>20</v>
       </c>
-      <c r="K25" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L25" s="6">
+      <c r="L25" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N25" s="6">
         <v>63000</v>
       </c>
-      <c r="M25" s="6">
+      <c r="O25" s="6">
         <v>2900</v>
       </c>
-      <c r="N25" s="6">
+      <c r="P25" s="6">
         <v>200000</v>
       </c>
-      <c r="O25" s="6">
+      <c r="Q25" s="6">
         <v>39000</v>
       </c>
-      <c r="P25" s="6">
+      <c r="R25" s="6">
         <v>1210</v>
       </c>
-      <c r="Q25" s="6">
+      <c r="S25" s="6">
         <v>5</v>
       </c>
-      <c r="R25" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="U25" s="11"/>
+      <c r="T25" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="W25" s="11"/>
     </row>
-    <row r="26" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C26" s="6">
         <v>10021</v>
       </c>
       <c r="D26" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="6">
+        <v>10022</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E26" s="6">
-        <v>10022</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G26" s="8">
+      <c r="H26" s="8">
         <v>345000</v>
       </c>
-      <c r="H26" s="6">
+      <c r="I26" s="6">
         <v>20</v>
       </c>
-      <c r="I26" s="8">
+      <c r="J26" s="8">
         <v>50</v>
       </c>
-      <c r="J26" s="6">
+      <c r="K26" s="6">
         <v>20</v>
       </c>
-      <c r="K26" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L26" s="6">
+      <c r="L26" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N26" s="6">
         <v>69000</v>
       </c>
-      <c r="M26" s="6">
+      <c r="O26" s="6">
         <v>3000</v>
       </c>
-      <c r="N26" s="6">
+      <c r="P26" s="6">
         <v>200000</v>
       </c>
-      <c r="O26" s="6">
+      <c r="Q26" s="6">
         <v>42000</v>
       </c>
-      <c r="P26" s="6">
+      <c r="R26" s="6">
         <v>1250</v>
       </c>
-      <c r="Q26" s="6">
+      <c r="S26" s="6">
         <v>5</v>
       </c>
-      <c r="R26" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="U26" s="11"/>
+      <c r="T26" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="W26" s="11"/>
     </row>
-    <row r="27" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C27" s="6">
         <v>10022</v>
       </c>
       <c r="D27" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F27" s="6">
+        <v>10023</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="6">
-        <v>10023</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="8">
+      <c r="H27" s="8">
         <v>393700</v>
       </c>
-      <c r="H27" s="6">
+      <c r="I27" s="6">
         <v>20</v>
       </c>
-      <c r="I27" s="8">
+      <c r="J27" s="8">
         <v>50</v>
       </c>
-      <c r="J27" s="6">
+      <c r="K27" s="6">
         <v>20</v>
       </c>
-      <c r="K27" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L27" s="6">
+      <c r="L27" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N27" s="6">
         <v>72000</v>
       </c>
-      <c r="M27" s="6">
+      <c r="O27" s="6">
         <v>3100</v>
       </c>
-      <c r="N27" s="6">
+      <c r="P27" s="6">
         <v>200000</v>
       </c>
-      <c r="O27" s="6">
+      <c r="Q27" s="6">
         <v>45000</v>
       </c>
-      <c r="P27" s="6">
+      <c r="R27" s="6">
         <v>1290</v>
       </c>
-      <c r="Q27" s="6">
+      <c r="S27" s="6">
         <v>6</v>
       </c>
-      <c r="R27" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="U27" s="11"/>
+      <c r="T27" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="W27" s="11"/>
     </row>
-    <row r="28" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C28" s="6">
         <v>10023</v>
       </c>
       <c r="D28" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F28" s="6">
+        <v>10024</v>
+      </c>
+      <c r="G28" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="6">
-        <v>10024</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G28" s="8">
+      <c r="H28" s="8">
         <v>444800</v>
       </c>
-      <c r="H28" s="6">
+      <c r="I28" s="6">
         <v>20</v>
       </c>
-      <c r="I28" s="8">
+      <c r="J28" s="8">
         <v>50</v>
       </c>
-      <c r="J28" s="6">
+      <c r="K28" s="6">
         <v>20</v>
       </c>
-      <c r="K28" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L28" s="6">
+      <c r="L28" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N28" s="6">
         <v>78000</v>
       </c>
-      <c r="M28" s="6">
+      <c r="O28" s="6">
         <v>3200</v>
       </c>
-      <c r="N28" s="6">
+      <c r="P28" s="6">
         <v>200000</v>
       </c>
-      <c r="O28" s="6">
+      <c r="Q28" s="6">
         <v>48000</v>
       </c>
-      <c r="P28" s="6">
+      <c r="R28" s="6">
         <v>1330</v>
       </c>
-      <c r="Q28" s="6">
+      <c r="S28" s="6">
         <v>6</v>
       </c>
-      <c r="R28" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="U28" s="11"/>
+      <c r="T28" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="W28" s="11"/>
     </row>
-    <row r="29" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="6">
         <v>10024</v>
       </c>
       <c r="D29" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" s="6">
+        <v>10025</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E29" s="6">
-        <v>10025</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G29" s="8">
+      <c r="H29" s="8">
         <v>508200</v>
       </c>
-      <c r="H29" s="6">
+      <c r="I29" s="6">
         <v>20</v>
       </c>
-      <c r="I29" s="8">
+      <c r="J29" s="8">
         <v>50</v>
       </c>
-      <c r="J29" s="6">
+      <c r="K29" s="6">
         <v>20</v>
       </c>
-      <c r="K29" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L29" s="6">
+      <c r="L29" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M29" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N29" s="6">
         <v>82500</v>
       </c>
-      <c r="M29" s="6">
+      <c r="O29" s="6">
         <v>3300</v>
       </c>
-      <c r="N29" s="6">
+      <c r="P29" s="6">
         <v>200000</v>
       </c>
-      <c r="O29" s="6">
+      <c r="Q29" s="6">
         <v>51000</v>
       </c>
-      <c r="P29" s="6">
+      <c r="R29" s="6">
         <v>1380</v>
       </c>
-      <c r="Q29" s="6">
+      <c r="S29" s="6">
         <v>6</v>
       </c>
-      <c r="R29" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="U29" s="11"/>
+      <c r="T29" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="W29" s="11"/>
     </row>
-    <row r="30" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C30" s="6">
         <v>10025</v>
       </c>
       <c r="D30" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F30" s="6">
+        <v>10026</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E30" s="6">
-        <v>10026</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G30" s="8">
-        <f>G29+100000</f>
+      <c r="H30" s="8">
+        <f>H29+100000</f>
         <v>608200</v>
       </c>
-      <c r="H30" s="6">
+      <c r="I30" s="6">
         <v>20</v>
       </c>
-      <c r="I30" s="8">
+      <c r="J30" s="8">
         <v>50</v>
       </c>
-      <c r="J30" s="6">
+      <c r="K30" s="6">
         <v>20</v>
       </c>
-      <c r="K30" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L30" s="6">
+      <c r="L30" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M30" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N30" s="6">
         <v>88500</v>
       </c>
-      <c r="M30" s="6">
+      <c r="O30" s="6">
         <v>3400</v>
       </c>
-      <c r="N30" s="6">
+      <c r="P30" s="6">
         <v>200000</v>
       </c>
-      <c r="O30" s="6">
+      <c r="Q30" s="6">
         <v>54000</v>
       </c>
-      <c r="P30" s="6">
+      <c r="R30" s="6">
         <v>1420</v>
       </c>
-      <c r="Q30" s="6">
+      <c r="S30" s="6">
         <v>7</v>
       </c>
-      <c r="R30" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="U30" s="11"/>
+      <c r="T30" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="W30" s="11"/>
     </row>
-    <row r="31" spans="3:21" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:23" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C31" s="13">
         <v>10026</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E31" s="13">
+        <v>124</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F31" s="13">
         <v>10027</v>
       </c>
-      <c r="F31" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G31" s="16">
+      <c r="G31" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H31" s="16">
         <v>800000</v>
       </c>
-      <c r="H31" s="13">
+      <c r="I31" s="13">
         <v>20</v>
       </c>
-      <c r="I31" s="16">
+      <c r="J31" s="16">
         <v>50</v>
       </c>
-      <c r="J31" s="13">
+      <c r="K31" s="13">
         <v>20</v>
       </c>
-      <c r="K31" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="L31" s="13">
-        <f>L30+6000</f>
+      <c r="L31" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="M31" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N31" s="13">
+        <f>N30+6000</f>
         <v>94500</v>
       </c>
-      <c r="M31" s="6">
+      <c r="O31" s="6">
         <v>3500</v>
       </c>
-      <c r="N31" s="13">
+      <c r="P31" s="13">
         <v>200000</v>
       </c>
-      <c r="O31" s="6">
+      <c r="Q31" s="6">
         <v>57000</v>
       </c>
-      <c r="P31" s="6">
+      <c r="R31" s="6">
         <v>1460</v>
       </c>
-      <c r="Q31" s="13">
+      <c r="S31" s="13">
         <v>7</v>
       </c>
-      <c r="R31" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="U31" s="18"/>
+      <c r="T31" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="W31" s="18"/>
     </row>
-    <row r="32" spans="3:21" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:23" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C32" s="13">
         <v>10027</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E32" s="13">
+        <v>125</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="F32" s="13">
         <v>10028</v>
       </c>
-      <c r="F32" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="G32" s="16">
-        <f>G31+200000</f>
+      <c r="G32" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="H32" s="16">
+        <f>H31+200000</f>
         <v>1000000</v>
       </c>
-      <c r="H32" s="13">
+      <c r="I32" s="13">
         <v>20</v>
       </c>
-      <c r="I32" s="16">
+      <c r="J32" s="16">
         <v>50</v>
       </c>
-      <c r="J32" s="13">
+      <c r="K32" s="13">
         <v>20</v>
       </c>
-      <c r="K32" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="L32" s="13">
-        <f t="shared" ref="L32:L35" si="0">L31+6000</f>
+      <c r="L32" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N32" s="13">
+        <f t="shared" ref="N32:N35" si="0">N31+6000</f>
         <v>100500</v>
       </c>
-      <c r="M32" s="6">
+      <c r="O32" s="6">
         <v>3600</v>
       </c>
-      <c r="N32" s="13">
+      <c r="P32" s="13">
         <v>200000</v>
       </c>
-      <c r="O32" s="6">
+      <c r="Q32" s="6">
         <v>60000</v>
       </c>
-      <c r="P32" s="6">
+      <c r="R32" s="6">
         <v>1500</v>
       </c>
-      <c r="Q32" s="13">
+      <c r="S32" s="13">
         <v>7</v>
       </c>
-      <c r="R32" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="U32" s="18"/>
+      <c r="T32" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="W32" s="18"/>
     </row>
-    <row r="33" spans="3:21" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:23" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C33" s="13">
         <v>10028</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E33" s="13">
+        <v>126</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F33" s="13">
         <v>10029</v>
       </c>
-      <c r="F33" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="G33" s="16">
-        <f t="shared" ref="G33:G34" si="1">G32+250000</f>
+      <c r="G33" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="H33" s="16">
+        <f t="shared" ref="H33:H34" si="1">H32+250000</f>
         <v>1250000</v>
       </c>
-      <c r="H33" s="13">
+      <c r="I33" s="13">
         <v>20</v>
       </c>
-      <c r="I33" s="16">
+      <c r="J33" s="16">
         <v>50</v>
       </c>
-      <c r="J33" s="13">
+      <c r="K33" s="13">
         <v>20</v>
       </c>
-      <c r="K33" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="L33" s="13">
+      <c r="L33" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N33" s="13">
         <f t="shared" si="0"/>
         <v>106500</v>
       </c>
-      <c r="M33" s="6">
+      <c r="O33" s="6">
         <v>3700</v>
       </c>
-      <c r="N33" s="13">
+      <c r="P33" s="13">
         <v>200000</v>
       </c>
-      <c r="O33" s="6">
+      <c r="Q33" s="6">
         <v>63000</v>
       </c>
-      <c r="P33" s="6">
+      <c r="R33" s="6">
         <v>1540</v>
       </c>
-      <c r="Q33" s="13">
+      <c r="S33" s="13">
         <v>8</v>
       </c>
-      <c r="R33" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="U33" s="18"/>
+      <c r="T33" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="W33" s="18"/>
     </row>
-    <row r="34" spans="3:21" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:23" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C34" s="13">
         <v>10029</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="E34" s="13">
+        <v>127</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F34" s="13">
         <v>10030</v>
       </c>
-      <c r="F34" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="G34" s="16">
+      <c r="G34" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="H34" s="16">
         <f t="shared" si="1"/>
         <v>1500000</v>
       </c>
-      <c r="H34" s="13">
+      <c r="I34" s="13">
         <v>20</v>
       </c>
-      <c r="I34" s="16">
+      <c r="J34" s="16">
         <v>50</v>
       </c>
-      <c r="J34" s="13">
+      <c r="K34" s="13">
         <v>20</v>
       </c>
-      <c r="K34" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="L34" s="13">
+      <c r="L34" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="M34" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N34" s="13">
         <f t="shared" si="0"/>
         <v>112500</v>
       </c>
-      <c r="M34" s="6">
+      <c r="O34" s="6">
         <v>3800</v>
       </c>
-      <c r="N34" s="13">
+      <c r="P34" s="13">
         <v>200000</v>
       </c>
-      <c r="O34" s="6">
+      <c r="Q34" s="6">
         <v>66000</v>
       </c>
-      <c r="P34" s="6">
+      <c r="R34" s="6">
         <v>1580</v>
       </c>
-      <c r="Q34" s="13">
+      <c r="S34" s="13">
         <v>8</v>
       </c>
-      <c r="R34" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="U34" s="18"/>
+      <c r="T34" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="W34" s="18"/>
     </row>
-    <row r="35" spans="3:21" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:23" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C35" s="13">
         <v>10030</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" s="19">
+        <v>128</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="F35" s="19">
         <v>0</v>
       </c>
-      <c r="F35" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="G35" s="16">
+      <c r="G35" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="H35" s="16">
         <v>0</v>
       </c>
-      <c r="H35" s="13">
+      <c r="I35" s="13">
         <v>20</v>
       </c>
-      <c r="I35" s="16">
+      <c r="J35" s="16">
         <v>50</v>
       </c>
-      <c r="J35" s="13">
+      <c r="K35" s="13">
         <v>20</v>
       </c>
-      <c r="K35" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="L35" s="13">
+      <c r="L35" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="M35" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="N35" s="13">
         <f t="shared" si="0"/>
         <v>118500</v>
       </c>
-      <c r="M35" s="6">
+      <c r="O35" s="6">
         <v>3900</v>
       </c>
-      <c r="N35" s="13">
+      <c r="P35" s="13">
         <v>200000</v>
       </c>
-      <c r="O35" s="6">
+      <c r="Q35" s="6">
         <v>69000</v>
       </c>
-      <c r="P35" s="6">
+      <c r="R35" s="6">
         <v>1620</v>
       </c>
-      <c r="Q35" s="13">
+      <c r="S35" s="13">
         <v>9</v>
       </c>
-      <c r="R35" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="U35" s="18"/>
+      <c r="T35" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="W35" s="18"/>
     </row>
-    <row r="36" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="3:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="3:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
